--- a/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="82">
   <si>
     <t>Dự án</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>Đường kính</t>
+  </si>
+  <si>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
@@ -1103,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1117,10 +1120,10 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1134,10 +1137,10 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1152,54 +1155,54 @@
     <row r="9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5">
         <v>4.1</v>
@@ -1222,19 +1225,19 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" s="5">
         <v>0</v>
@@ -1257,19 +1260,19 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>29</v>
-      </c>
       <c r="E13" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="9">
         <v>-2</v>
@@ -1292,19 +1295,19 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14" s="9">
         <v>-4</v>
@@ -1327,19 +1330,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15" s="9">
         <v>-6</v>
@@ -1362,19 +1365,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="9">
         <v>-8</v>
@@ -1397,19 +1400,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" s="9">
         <v>-10</v>
@@ -1432,19 +1435,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F18" s="12">
         <v>-12</v>
@@ -1467,19 +1470,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" s="12">
         <v>-14</v>
@@ -1502,19 +1505,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="12">
         <v>-16</v>
@@ -1537,19 +1540,19 @@
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F21" s="12">
         <v>-18</v>
@@ -1572,19 +1575,19 @@
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>44</v>
-      </c>
       <c r="E22" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F22" s="16">
         <v>-20</v>
@@ -1607,19 +1610,19 @@
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" s="16">
         <v>-22</v>
@@ -1642,19 +1645,19 @@
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F24" s="16">
         <v>-24</v>
@@ -1677,19 +1680,19 @@
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F25" s="16">
         <v>-26</v>
@@ -1712,19 +1715,19 @@
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>50</v>
-      </c>
       <c r="E26" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F26" s="19">
         <v>-28</v>
@@ -1747,19 +1750,19 @@
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F27" s="19">
         <v>-30</v>
@@ -1782,19 +1785,19 @@
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F28" s="19">
         <v>-32</v>
@@ -1817,19 +1820,19 @@
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>55</v>
-      </c>
       <c r="E29" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F29" s="22">
         <v>-34</v>
@@ -1852,19 +1855,19 @@
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F30" s="22">
         <v>-36</v>
@@ -1887,19 +1890,19 @@
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F31" s="22">
         <v>-38</v>
@@ -1922,19 +1925,19 @@
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F32" s="22">
         <v>-40</v>
@@ -1957,19 +1960,19 @@
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F33" s="22">
         <v>-42</v>
@@ -1992,19 +1995,19 @@
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>62</v>
-      </c>
       <c r="E34" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F34" s="22">
         <v>-44</v>
@@ -2027,19 +2030,19 @@
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F35" s="22">
         <v>-46</v>
@@ -2062,19 +2065,19 @@
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F36" s="22">
         <v>-48</v>
@@ -2097,19 +2100,19 @@
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F37" s="22">
         <v>-50</v>
@@ -2132,19 +2135,19 @@
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F38" s="22">
         <v>-52</v>
@@ -2167,19 +2170,19 @@
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F39" s="22">
         <v>-54</v>
@@ -2202,19 +2205,19 @@
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F40" s="22">
         <v>-55</v>
@@ -2237,7 +2240,7 @@
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B43" s="26"/>
       <c r="C43" s="26"/>
@@ -2343,31 +2346,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2375,10 +2378,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5">
         <v>2</v>
@@ -2404,10 +2407,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>5</v>
@@ -2433,10 +2436,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="12">
         <v>4</v>
@@ -2462,10 +2465,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="16">
         <v>4</v>
@@ -2491,10 +2494,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="19">
         <v>3</v>
@@ -2520,10 +2523,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" s="22">
         <v>12</v>
@@ -2546,7 +2549,7 @@
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>5</v>

--- a/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>SGCT-KCN0001</t>
+    <t>SGCT-KCN0002</t>
   </si>
   <si>
     <t>Đường kính</t>

--- a/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TP03</t>
+    <t>TP-03 (GA1)</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1200</t>
+    <t>D1500</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="81">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TP-03 (GA1)</t>
+    <t>GA-1</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -143,7 +143,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét pha màu xám ghi, xám vàng, trạng thái dẻo cứng đến nửa cứng</t>
+    <t>Sét pha, xám xanh, xám đen, xám ghi, xám vàng, nâu đỏ, TT dẻo cứng đến nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">13:00
@@ -169,7 +169,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Cát pha màu xám vàng, trạng thái dẻo/Cát pha màu xám vàng, trạng thái dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">14:32
@@ -189,9 +189,6 @@
   </si>
   <si>
     <t>TK</t>
-  </si>
-  <si>
-    <t>Sét pha màu xám ghi, xám đen, trạng thái dẻo cứng đến nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">15:31
@@ -1721,13 +1718,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D26" s="21" t="s">
         <v>51</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F26" s="19">
         <v>-28</v>
@@ -1756,13 +1753,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="E27" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="F27" s="19">
         <v>-30</v>
@@ -1791,13 +1788,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D28" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="21" t="s">
         <v>55</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>56</v>
       </c>
       <c r="F28" s="19">
         <v>-32</v>
@@ -1820,19 +1817,19 @@
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="23" t="s">
+      <c r="D29" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>58</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>59</v>
       </c>
       <c r="F29" s="22">
         <v>-34</v>
@@ -1855,19 +1852,19 @@
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="23" t="s">
+      <c r="D30" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="E30" s="24" t="s">
         <v>59</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>60</v>
       </c>
       <c r="F30" s="22">
         <v>-36</v>
@@ -1890,19 +1887,19 @@
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>58</v>
-      </c>
       <c r="D31" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="24" t="s">
         <v>60</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>61</v>
       </c>
       <c r="F31" s="22">
         <v>-38</v>
@@ -1925,19 +1922,19 @@
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>58</v>
-      </c>
       <c r="D32" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="24" t="s">
         <v>61</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>62</v>
       </c>
       <c r="F32" s="22">
         <v>-40</v>
@@ -1960,19 +1957,19 @@
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B33" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>58</v>
-      </c>
       <c r="D33" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="24" t="s">
         <v>62</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>63</v>
       </c>
       <c r="F33" s="22">
         <v>-42</v>
@@ -1995,19 +1992,19 @@
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="24" t="s">
         <v>64</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>65</v>
       </c>
       <c r="F34" s="22">
         <v>-44</v>
@@ -2030,19 +2027,19 @@
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B35" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" s="24" t="s">
+      <c r="E35" s="24" t="s">
         <v>65</v>
-      </c>
-      <c r="E35" s="24" t="s">
-        <v>66</v>
       </c>
       <c r="F35" s="22">
         <v>-46</v>
@@ -2065,19 +2062,19 @@
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D36" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="24" t="s">
         <v>66</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>67</v>
       </c>
       <c r="F36" s="22">
         <v>-48</v>
@@ -2100,19 +2097,19 @@
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D37" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="24" t="s">
         <v>67</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>68</v>
       </c>
       <c r="F37" s="22">
         <v>-50</v>
@@ -2135,19 +2132,19 @@
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B38" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D38" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E38" s="24" t="s">
         <v>68</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>69</v>
       </c>
       <c r="F38" s="22">
         <v>-52</v>
@@ -2170,19 +2167,19 @@
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B39" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D39" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="24" t="s">
         <v>69</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>70</v>
       </c>
       <c r="F39" s="22">
         <v>-54</v>
@@ -2205,19 +2202,19 @@
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B40" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D40" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="24" t="s">
         <v>70</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>71</v>
       </c>
       <c r="F40" s="22">
         <v>-55</v>
@@ -2240,7 +2237,7 @@
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B43" s="26"/>
       <c r="C43" s="26"/>
@@ -2346,31 +2343,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2497,7 +2494,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
         <v>3</v>
@@ -2526,7 +2523,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" s="22">
         <v>12</v>
@@ -2549,7 +2546,7 @@
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>5</v>

--- a/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/ae984600-5d6b-447d-8113-f0c602acd48e_BienBan_TP03_21-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>GA-1</t>
+    <t>P14</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
